--- a/TASK1.xlsx
+++ b/TASK1.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASDC7\Desktop\github.p\Data-analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5751E0B7-E730-4F85-A518-F9DC434AFCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B3953B5-357F-4A8F-A2C7-3ED1FC0DC266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2FB6AEA2-7932-4542-82B9-AB46A7F6D890}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2FB6AEA2-7932-4542-82B9-AB46A7F6D890}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="72">
   <si>
     <t>Employee ID</t>
   </si>
@@ -152,6 +153,105 @@
   </si>
   <si>
     <t>Financ</t>
+  </si>
+  <si>
+    <t>Laptop Dell Inspiron 15</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>Ramesh</t>
+  </si>
+  <si>
+    <t>HP Wireless Mouse</t>
+  </si>
+  <si>
+    <t>West</t>
+  </si>
+  <si>
+    <t>Sneha</t>
+  </si>
+  <si>
+    <t>Samsung 24-inch Monitor</t>
+  </si>
+  <si>
+    <t>East</t>
+  </si>
+  <si>
+    <t>Arjun</t>
+  </si>
+  <si>
+    <t>Lenovo ThinkPad E14 Laptop</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>Kavita</t>
+  </si>
+  <si>
+    <t>oppoa78</t>
+  </si>
+  <si>
+    <t>iphone5</t>
+  </si>
+  <si>
+    <t>iphone6</t>
+  </si>
+  <si>
+    <t>iphone7</t>
+  </si>
+  <si>
+    <t>iphone8</t>
+  </si>
+  <si>
+    <t>iphone9</t>
+  </si>
+  <si>
+    <t>iphone10</t>
+  </si>
+  <si>
+    <t>iphone11</t>
+  </si>
+  <si>
+    <t>iphone12</t>
+  </si>
+  <si>
+    <t>iphone12max</t>
+  </si>
+  <si>
+    <t>iphone12promax</t>
+  </si>
+  <si>
+    <t>iphone13</t>
+  </si>
+  <si>
+    <t>iphone14</t>
+  </si>
+  <si>
+    <t>iphone15</t>
+  </si>
+  <si>
+    <t>iphone16</t>
+  </si>
+  <si>
+    <t>iphone17</t>
+  </si>
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Sales Amount</t>
+  </si>
+  <si>
+    <t>Salesperson</t>
+  </si>
+  <si>
+    <t>Monthly Sales Report</t>
   </si>
 </sst>
 </file>
@@ -159,9 +259,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="&quot;₹&quot;\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,8 +288,21 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -211,6 +324,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -242,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -266,11 +385,38 @@
     <xf numFmtId="14" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -957,4 +1103,326 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FF30DC1-990D-4BBC-9B5A-2CFCAF6ECB44}">
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="33.75" x14ac:dyDescent="0.5">
+      <c r="A1" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+    </row>
+    <row r="2" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="14">
+        <v>45000</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="17">
+        <v>1200</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="14">
+        <v>18000</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="17">
+        <v>62000</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="14">
+        <v>14431</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="17">
+        <v>43834</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="14">
+        <v>57163</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="17">
+        <v>41287</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="14">
+        <v>47735</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="17">
+        <v>46689</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="14">
+        <v>35914</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="17">
+        <v>61263</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="14">
+        <v>55533</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="17">
+        <v>44563</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="14">
+        <v>18370</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="17">
+        <v>36741</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="14">
+        <v>29477</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="17">
+        <v>61680</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="14">
+        <v>30436</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="17">
+        <v>68209</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>